--- a/output/casestudy_20260916.xlsx
+++ b/output/casestudy_20260916.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.674219399999856</v>
+        <v>9.270510700000159</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.225346499999887</v>
+        <v>9.241579700001239</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.011452799999915</v>
+        <v>6.418413900000814</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.474919600000248</v>
+        <v>10.05697719999989</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.12400609999986</v>
+        <v>10.11446290000094</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.918365999999878</v>
+        <v>7.879016099999717</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.825983599999745</v>
+        <v>9.71125419999953</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9.766823100000238</v>
+        <v>9.724890499999674</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>13.4402270999999</v>
+        <v>13.65203979999933</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.037370499999724</v>
+        <v>7.011734300000171</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,59 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.087558799999897</v>
+        <v>6.048758299999463</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R4 용인 실측 역률 100</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>general_a_2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-08-28 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>476.02327</v>
+      </c>
+      <c r="E13" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="F13" t="n">
+        <v>132</v>
+      </c>
+      <c r="G13" t="n">
+        <v>41.08229342532648</v>
+      </c>
+      <c r="H13" t="n">
+        <v>100.8144862191238</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12298296.07741935</v>
+      </c>
+      <c r="J13" t="n">
+        <v>49597412.23</v>
+      </c>
+      <c r="K13" t="n">
+        <v>61895708.30741935</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19.86938418466272</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>13.76329249999981</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,9 +2592,137 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>R4 용인 실측 역률 100</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>132</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>500</v>
+      </c>
+      <c r="C47" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="D47" t="n">
+        <v>28.80135248983531</v>
+      </c>
+      <c r="E47" t="n">
+        <v>465585.7548272483</v>
+      </c>
+      <c r="F47" t="n">
+        <v>120</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1371755.161290321</v>
+      </c>
+      <c r="H47" t="n">
+        <v>21832794.0374309</v>
+      </c>
+      <c r="I47" t="n">
+        <v>23190831.64710832</v>
+      </c>
+      <c r="J47" t="n">
+        <v>23190831.64710833</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.68075433387349</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1102769.252304211</v>
+      </c>
+      <c r="F48" t="n">
+        <v>120</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1421135.161290321</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23715557.01062761</v>
+      </c>
+      <c r="I48" t="n">
+        <v>25122480.82030503</v>
+      </c>
+      <c r="J48" t="n">
+        <v>25122480.82030503</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8.179882063646165</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2401738.820199978</v>
+      </c>
+      <c r="F49" t="n">
+        <v>120</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1421135.161290321</v>
+      </c>
+      <c r="H49" t="n">
+        <v>24660958.77724204</v>
+      </c>
+      <c r="I49" t="n">
+        <v>26067882.58691946</v>
+      </c>
+      <c r="J49" t="n">
+        <v>26067882.58691947</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A46:A49"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="A2:A5"/>
@@ -2564,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I232"/>
+  <dimension ref="A1:I253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9203,11 +9383,611 @@
       </c>
       <c r="I232" t="inlineStr"/>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>R4 용인 실측 역률 100</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>500</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1371755.161290321</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1019989.032258064</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1421135.161290321</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>28.22716233887541</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>21832794.0374309</v>
+      </c>
+      <c r="E234" t="n">
+        <v>19707849.27224809</v>
+      </c>
+      <c r="F234" t="n">
+        <v>23383003.92461409</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>15.71720495884344</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>23190831.64710832</v>
+      </c>
+      <c r="E235" t="n">
+        <v>20717638.41418357</v>
+      </c>
+      <c r="F235" t="n">
+        <v>24789927.73429151</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>16.42719318812214</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>23190831.64710833</v>
+      </c>
+      <c r="E236" t="n">
+        <v>20717638.41418357</v>
+      </c>
+      <c r="F236" t="n">
+        <v>24789927.73429151</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>16.42719318812214</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>120</v>
+      </c>
+      <c r="E237" t="n">
+        <v>120</v>
+      </c>
+      <c r="F237" t="n">
+        <v>122</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="E238" t="n">
+        <v>653917.3979531642</v>
+      </c>
+      <c r="F238" t="n">
+        <v>653931.4335780952</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1421135.161290321</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1019989.032258064</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1421135.161290321</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>28.22716233887541</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>23715557.01062761</v>
+      </c>
+      <c r="E241" t="n">
+        <v>21181957.19322234</v>
+      </c>
+      <c r="F241" t="n">
+        <v>25237507.33343017</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>16.06953526204924</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>25122480.82030503</v>
+      </c>
+      <c r="E242" t="n">
+        <v>22191746.33515783</v>
+      </c>
+      <c r="F242" t="n">
+        <v>26644431.14310759</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>16.71150261769272</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>25122480.82030503</v>
+      </c>
+      <c r="E243" t="n">
+        <v>22191746.33515783</v>
+      </c>
+      <c r="F243" t="n">
+        <v>26644431.14310758</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>16.71150261769271</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>120</v>
+      </c>
+      <c r="E244" t="n">
+        <v>120</v>
+      </c>
+      <c r="F244" t="n">
+        <v>122</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1307834.795906328</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1307862.86715619</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>2838081.612903226</v>
+      </c>
+      <c r="E247" t="n">
+        <v>2488601.935483871</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2838081.612903226</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>12.31394036839743</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>23272029.67227682</v>
+      </c>
+      <c r="E248" t="n">
+        <v>20452277.86005339</v>
+      </c>
+      <c r="F248" t="n">
+        <v>24555709.08009543</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>16.71070139598712</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>26081730.46905101</v>
+      </c>
+      <c r="E249" t="n">
+        <v>22915993.77618242</v>
+      </c>
+      <c r="F249" t="n">
+        <v>27365409.87686963</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>16.25927081197507</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>26081730.46905101</v>
+      </c>
+      <c r="E250" t="n">
+        <v>22915993.77618242</v>
+      </c>
+      <c r="F250" t="n">
+        <v>27365409.87686963</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>16.25927081197506</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>120</v>
+      </c>
+      <c r="E251" t="n">
+        <v>120</v>
+      </c>
+      <c r="F251" t="n">
+        <v>122</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="E252" t="n">
+        <v>2615669.591812657</v>
+      </c>
+      <c r="F252" t="n">
+        <v>2615725.734312381</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="48">
     <mergeCell ref="A44:A64"/>
     <mergeCell ref="B86:B92"/>
     <mergeCell ref="B58:B64"/>
+    <mergeCell ref="B240:B246"/>
     <mergeCell ref="B44:B50"/>
     <mergeCell ref="B9:B15"/>
     <mergeCell ref="B23:B29"/>
@@ -9237,9 +10017,11 @@
     <mergeCell ref="A149:A169"/>
     <mergeCell ref="B184:B190"/>
     <mergeCell ref="A86:A106"/>
+    <mergeCell ref="A233:A253"/>
     <mergeCell ref="B72:B78"/>
     <mergeCell ref="A2:A22"/>
     <mergeCell ref="B100:B106"/>
+    <mergeCell ref="B233:B239"/>
     <mergeCell ref="B149:B155"/>
     <mergeCell ref="B156:B162"/>
     <mergeCell ref="B170:B176"/>
@@ -9247,6 +10029,7 @@
     <mergeCell ref="B2:B8"/>
     <mergeCell ref="B93:B99"/>
     <mergeCell ref="A23:A43"/>
+    <mergeCell ref="B247:B253"/>
     <mergeCell ref="B191:B197"/>
     <mergeCell ref="B219:B225"/>
   </mergeCells>
@@ -9260,7 +10043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9841,8 +10624,77 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>R4 용인 실측 역률 100</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>62834646.96745159</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-938938.6600322425</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>61895708.30741935</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>68767267.06845161</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-6871558.761032261</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>68174551.75541934</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-6278843.447999991</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A17:A19"/>
@@ -9852,6 +10704,7 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A33:A36"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9864,7 +10717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11121,12 +11974,123 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>R4 용인 실측 역률 100</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>II → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7.2 계약전력 조정</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>계약 290 kW (실제 값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7.4 역률 개선 (92→97%)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>124225.2129032239</v>
+      </c>
+      <c r="D59" t="n">
+        <v>124225.2129032239</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>요금표와 약관만으로 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>최소 규격 미달 — 필요 출력 25.3 kW &lt; 상업용 최소 50 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>거래 가능일 244일 · 등록 권장 28 kW · 연간 감축 5,882 kWh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A57:A61"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A52:A56"/>
     <mergeCell ref="A42:A46"/>
@@ -11145,7 +12109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13846,12 +14810,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>교차</t>
+          <t>R4 용인 실측 역률 100</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -13861,14 +14825,14 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>C1 95.0 kW vs C2 5.0 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -13878,14 +14842,14 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.0 kW)</t>
+          <t>0 → 21,832,794 → 23,715,557 → 24,660,959</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -13895,14 +14859,14 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>저감률 C5 0.29% vs C1 1.79% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+          <t>증분 1,371,755 → 49,380 → 0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -13912,14 +14876,14 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>관측 10,920.6 kW vs 요금적용 3,604.0 kW (67.0% 낮다)</t>
+          <t>132.0 → 120.0 → 120.0 → 120.0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>C6 야간 피크형: 하한이 요금적용전력을 붙들어 PV 가 한 칸도 못 내린다</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -13929,41 +14893,285 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>C6 저감 0.00 kW vs C1 95.00 kW — 경부하 최대라 대상 수요가 하한 3,603.8 kW 아래에 있다</t>
+          <t>최대 편차 0.002%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
+          <t>기준값이 범위 안에 있음</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>벗어난 지표 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 상한: 평탄형</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0 원 · II → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>124,225 원 (기본요금 12,422,521 의 1.00%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>244 / 365일</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>viable=False · 목표 0 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>목표 0 kW · 절감액 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>교차</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>C1 95.0 kW vs C2 5.0 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.0 kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>저감률 C5 0.29% vs C1 1.79% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>관측 10,920.6 kW vs 요금적용 3,604.0 kW (67.0% 낮다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형: 하한이 요금적용전력을 붙들어 PV 가 한 칸도 못 내린다</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>C6 저감 0.00 kW vs C1 95.00 kW — 경부하 최대라 대상 수요가 하한 3,603.8 kW 아래에 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
           <t>C4 산업용(을) 주말 할인이 PV 최성기와 겹쳐 전력량요금 절감 비율이 낮다</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
         <is>
           <t>C4 4.95% vs C1 5.44% (봄·가을 토·일·공휴일 11~14시 할인 구간의 단가가 이미 낮다)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A30:A43"/>
     <mergeCell ref="A44:A57"/>
     <mergeCell ref="A16:A29"/>
     <mergeCell ref="A114:A127"/>
     <mergeCell ref="A128:A141"/>
     <mergeCell ref="A142:A155"/>
+    <mergeCell ref="A156:A169"/>
+    <mergeCell ref="A170:A175"/>
     <mergeCell ref="A100:A113"/>
     <mergeCell ref="A72:A85"/>
     <mergeCell ref="A86:A99"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A58:A71"/>
-    <mergeCell ref="A156:A161"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13975,7 +15183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13998,7 +15206,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>9.3 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +15230,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.0 초</t>
+          <t>6.4 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +15242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.5 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +15278,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +15290,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +15302,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13.4 초</t>
+          <t>13.7 초</t>
         </is>
       </c>
     </row>
@@ -14118,43 +15326,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>6.0 초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>전체 소요</t>
+          <t>R4 용인 실측 역률 100 소요</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>105.4 초</t>
+          <t>13.8 초</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>기상 취득 호출</t>
+          <t>전체 소요</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0 회</t>
+          <t>121.7 초</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>기상 취득 호출</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0 회</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>기상 캐시 적중</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>11/11 (C1~C8 은 좌표·기간이 같아 첫 건만 취득한다. 실측 R1~R3 도 서로 같아 그중 첫 건만 취득한다)</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12/12 (C1~C8 은 좌표·기간이 같아 첫 건만 취득한다. 실측 R1~R4 도 서로 같아 그중 첫 건만 취득한다)</t>
         </is>
       </c>
     </row>
